--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_nuble.xlsx
@@ -90,12 +90,12 @@
     <t xml:space="preserve">El Carmen</t>
   </si>
   <si>
+    <t xml:space="preserve">Coelemu</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ranquil</t>
   </si>
   <si>
-    <t xml:space="preserve">Coelemu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ñiquén</t>
   </si>
   <si>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:15</t>
+    <t xml:space="preserve">2026-09-10 00:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -844,7 +844,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>16206</v>
+        <v>16203</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -857,7 +857,7 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>16203</v>
+        <v>16206</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:20</t>
+    <t xml:space="preserve">2026-09-18 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
